--- a/output/yearly_surface_area_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_42_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631356489</v>
+        <v>10.84497614224449</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890718769234</v>
+        <v>37.78907127996138</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.804092427507142</v>
+        <v>4.584761778832605</v>
       </c>
       <c r="C2" t="n">
-        <v>8.376271412633786</v>
+        <v>7.061711236647307</v>
       </c>
       <c r="D2" t="n">
-        <v>14.34726094986289</v>
+        <v>36.51021537323463</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.42111301185965</v>
+        <v>14.06844460185679</v>
       </c>
       <c r="C3" t="n">
-        <v>11.85460352878024</v>
+        <v>32.22586839190155</v>
       </c>
       <c r="D3" t="n">
-        <v>52.72476045657496</v>
+        <v>83.27184027421447</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.58621085708914</v>
+        <v>30.84749461513903</v>
       </c>
       <c r="C4" t="n">
-        <v>47.43903081691013</v>
+        <v>92.67011104696917</v>
       </c>
       <c r="D4" t="n">
-        <v>70.57784245830319</v>
+        <v>110.6910719061236</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.80482179996669</v>
+        <v>41.03705403751668</v>
       </c>
       <c r="C5" t="n">
-        <v>106.666888066416</v>
+        <v>145.3232039211341</v>
       </c>
       <c r="D5" t="n">
-        <v>55.27239574909544</v>
+        <v>75.91364123088462</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.9548082145382</v>
+        <v>38.07806645691679</v>
       </c>
       <c r="C6" t="n">
-        <v>146.838040628787</v>
+        <v>149.6154048841012</v>
       </c>
       <c r="D6" t="n">
-        <v>42.18373535607696</v>
+        <v>47.65796055495717</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.03933632809466</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>138.5177288352952</v>
+        <v>130.6126963206999</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>13.4352173326176</v>
       </c>
       <c r="C8" t="n">
-        <v>97.05066930331843</v>
+        <v>89.45685081096936</v>
       </c>
       <c r="D8" t="n">
-        <v>35.46563581591602</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>46.81562102471339</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.672216038024421</v>
+        <v>7.64916522234835</v>
       </c>
       <c r="C21" t="n">
-        <v>94.94367347055221</v>
+        <v>92.74612832097372</v>
       </c>
       <c r="D21" t="n">
-        <v>7.672216038024421</v>
+        <v>7.64916522234835</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.841218913819274</v>
+        <v>5.201299337099601</v>
       </c>
       <c r="C2" t="n">
-        <v>6.177156555120932</v>
+        <v>5.795256698168921</v>
       </c>
       <c r="D2" t="n">
-        <v>18.98307360931632</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.35868206941536</v>
+        <v>14.46114368355552</v>
       </c>
       <c r="C3" t="n">
-        <v>22.44275251908209</v>
+        <v>29.66841562233861</v>
       </c>
       <c r="D3" t="n">
-        <v>51.76264770641308</v>
+        <v>90.51222959303469</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.41654843070368</v>
+        <v>28.44810322595982</v>
       </c>
       <c r="C4" t="n">
-        <v>38.46683854779853</v>
+        <v>85.84205576393261</v>
       </c>
       <c r="D4" t="n">
-        <v>79.28201760415543</v>
+        <v>123.568656542729</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.00179323562181</v>
+        <v>43.07418052382881</v>
       </c>
       <c r="C5" t="n">
-        <v>96.30944978661212</v>
+        <v>156.8096520608218</v>
       </c>
       <c r="D5" t="n">
-        <v>65.40894079544375</v>
+        <v>92.57880851047423</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.81017250684443</v>
+        <v>45.8466360406218</v>
       </c>
       <c r="C6" t="n">
-        <v>156.6191930061979</v>
+        <v>184.2318289358437</v>
       </c>
       <c r="D6" t="n">
-        <v>49.02651685467723</v>
+        <v>57.60011955586462</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.86074036137975</v>
+        <v>34.19525428662065</v>
       </c>
       <c r="C7" t="n">
-        <v>174.4496948107285</v>
+        <v>169.2994463542497</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.61732368398877</v>
+        <v>19.69385894719101</v>
       </c>
       <c r="C8" t="n">
-        <v>137.4397698560322</v>
+        <v>125.6735236206342</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>84.42343033129593</v>
+        <v>74.54999366968578</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>45.69544689416779</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.852615408449529</v>
+        <v>7.816576125314478</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0655772359001</v>
+        <v>100.6384176134239</v>
       </c>
       <c r="D21" t="n">
-        <v>8.834192334505721</v>
+        <v>8.793648140978787</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.946265918173683</v>
+        <v>6.346017160251383</v>
       </c>
       <c r="C2" t="n">
-        <v>14.25399491795944</v>
+        <v>10.70399521940297</v>
       </c>
       <c r="D2" t="n">
-        <v>23.07597978832128</v>
+        <v>30.56278778090745</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.61317570899353</v>
+        <v>15.4968875115359</v>
       </c>
       <c r="C3" t="n">
-        <v>22.99743997198154</v>
+        <v>26.19793748782614</v>
       </c>
       <c r="D3" t="n">
-        <v>53.88813148610743</v>
+        <v>93.9876164660684</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.45934441906305</v>
+        <v>27.19735665074939</v>
       </c>
       <c r="C4" t="n">
-        <v>46.07341976030281</v>
+        <v>80.4561878584346</v>
       </c>
       <c r="D4" t="n">
-        <v>85.35707239803469</v>
+        <v>133.6384427451886</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.61538555077607</v>
+        <v>42.5096755938869</v>
       </c>
       <c r="C5" t="n">
-        <v>84.65119579868124</v>
+        <v>155.2879431192393</v>
       </c>
       <c r="D5" t="n">
-        <v>75.32459260833654</v>
+        <v>108.3604028562417</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.53219903782235</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C6" t="n">
-        <v>154.2040936537508</v>
+        <v>208.8658423308047</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>69.51460969460392</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.3228247349105</v>
+        <v>41.9206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>198.4642254043097</v>
+        <v>209.2438151969397</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.21252483466959</v>
+        <v>26.36974333606933</v>
       </c>
       <c r="C8" t="n">
-        <v>177.4116276344411</v>
+        <v>164.3102045212674</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>121.0328022226595</v>
+        <v>106.3890534661141</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>68.89905388404117</v>
+        <v>60.07314202286233</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>41.40324593120072</v>
+        <v>39.09319358310798</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.018630083426434</v>
+        <v>7.96795429162639</v>
       </c>
       <c r="C21" t="n">
-        <v>111.2584924075418</v>
+        <v>107.5673829369563</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02328760428304</v>
+        <v>9.959942864532987</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.287513208624073</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="C2" t="n">
-        <v>9.691813336324511</v>
+        <v>7.534913630094269</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87409961414493</v>
+        <v>25.35167096676538</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.09838005906971</v>
+        <v>18.41758693167016</v>
       </c>
       <c r="C3" t="n">
-        <v>37.77274292089603</v>
+        <v>43.65341166933442</v>
       </c>
       <c r="D3" t="n">
-        <v>59.43009727658066</v>
+        <v>101.9986777327224</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.79796526157018</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="C4" t="n">
-        <v>67.91043394586461</v>
+        <v>119.9950948992706</v>
       </c>
       <c r="D4" t="n">
-        <v>83.60857973677112</v>
+        <v>125.4320136853895</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.52668410002858</v>
+        <v>28.34796496012666</v>
       </c>
       <c r="C5" t="n">
-        <v>92.13702204356316</v>
+        <v>124.8046769023758</v>
       </c>
       <c r="D5" t="n">
-        <v>54.14338588921161</v>
+        <v>69.60591223109887</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.83905979642831</v>
+        <v>26.00256969468102</v>
       </c>
       <c r="C6" t="n">
-        <v>130.6971266232651</v>
+        <v>137.8216697129843</v>
       </c>
       <c r="D6" t="n">
-        <v>29.42396044398116</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>124.7438085447125</v>
+        <v>115.5212706110179</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>89.20650514638642</v>
+        <v>78.35819301445918</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>28.32833000604172</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.347178834404876</v>
+        <v>3.495021827118645</v>
       </c>
       <c r="C2" t="n">
-        <v>4.012402867256714</v>
+        <v>3.355613653115598</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0955326269482</v>
+        <v>18.42740440871263</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.84941705281852</v>
+        <v>19.74785507092459</v>
       </c>
       <c r="C3" t="n">
-        <v>38.65140711619693</v>
+        <v>37.394770054761</v>
       </c>
       <c r="D3" t="n">
-        <v>60.75545667731387</v>
+        <v>99.45595117872313</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.30168394930681</v>
+        <v>26.44435616159208</v>
       </c>
       <c r="C4" t="n">
-        <v>83.35332533366693</v>
+        <v>118.0806868759894</v>
       </c>
       <c r="D4" t="n">
-        <v>93.56350145783378</v>
+        <v>144.1421614329252</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.79099521664922</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="C5" t="n">
-        <v>110.4957041129785</v>
+        <v>169.8914402199105</v>
       </c>
       <c r="D5" t="n">
-        <v>66.83247496660162</v>
+        <v>88.57818661566847</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.99756314516856</v>
+        <v>30.5510068084565</v>
       </c>
       <c r="C6" t="n">
-        <v>144.4229412763398</v>
+        <v>166.7223586306019</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>16.16938468894497</v>
       </c>
       <c r="C7" t="n">
-        <v>154.8068867441583</v>
+        <v>148.4589060884984</v>
       </c>
       <c r="D7" t="n">
         <v>30.54217107911827</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>115.5762484824558</v>
+        <v>101.8906854852552</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>59.46249495082079</v>
+        <v>49.81093327037041</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.279438242811846</v>
+        <v>3.270201602846125</v>
       </c>
       <c r="C2" t="n">
-        <v>9.240209392370978</v>
+        <v>5.21406205725481</v>
       </c>
       <c r="D2" t="n">
-        <v>10.52335364182156</v>
+        <v>17.08830054011998</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24854640009046</v>
+        <v>15.82577299245858</v>
       </c>
       <c r="C3" t="n">
-        <v>26.31574721233575</v>
+        <v>25.01493150420873</v>
       </c>
       <c r="D3" t="n">
-        <v>57.8347572571796</v>
+        <v>92.73097940463248</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.38499363544754</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>90.1686178965483</v>
+        <v>105.8029500866787</v>
       </c>
       <c r="D4" t="n">
-        <v>100.3277431400943</v>
+        <v>155.9476775764931</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.30136515413732</v>
+        <v>34.7538687303371</v>
       </c>
       <c r="C5" t="n">
-        <v>133.1495323884737</v>
+        <v>192.152569413707</v>
       </c>
       <c r="D5" t="n">
-        <v>83.25220532012953</v>
+        <v>114.8399377042707</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.59254331167113</v>
+        <v>35.30070220160257</v>
       </c>
       <c r="C6" t="n">
-        <v>159.5978155408827</v>
+        <v>215.1048489912932</v>
       </c>
       <c r="D6" t="n">
-        <v>46.49066253460771</v>
+        <v>53.93721887131977</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78171751895449</v>
+        <v>23.89475737366311</v>
       </c>
       <c r="C7" t="n">
-        <v>182.7140469850781</v>
+        <v>190.7987393295506</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>157.8012172421111</v>
+        <v>142.9473744768568</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>95.96092935160446</v>
+        <v>80.42968067041991</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.46605242207675</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.531927329252524</v>
+        <v>1.980185119465816</v>
       </c>
       <c r="C2" t="n">
-        <v>4.264712027248144</v>
+        <v>2.564325003492669</v>
       </c>
       <c r="D2" t="n">
-        <v>7.268860002243384</v>
+        <v>11.93412509282423</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96874830438012</v>
+        <v>15.39380400258999</v>
       </c>
       <c r="C3" t="n">
-        <v>32.30931694676253</v>
+        <v>24.67131980772234</v>
       </c>
       <c r="D3" t="n">
-        <v>55.86144437164351</v>
+        <v>89.89372853935919</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.43077592464865</v>
+        <v>34.86775146402972</v>
       </c>
       <c r="C4" t="n">
-        <v>89.63258365002955</v>
+        <v>101.2338962711141</v>
       </c>
       <c r="D4" t="n">
-        <v>107.3089510649934</v>
+        <v>167.1916340332318</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.65755964432967</v>
+        <v>36.57010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>163.1910121384261</v>
+        <v>226.9800692218626</v>
       </c>
       <c r="D5" t="n">
-        <v>89.58447801252146</v>
+        <v>120.5340743889022</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>28.53842401475054</v>
       </c>
       <c r="C6" t="n">
-        <v>198.4406634594078</v>
+        <v>247.8294452169521</v>
       </c>
       <c r="D6" t="n">
-        <v>45.88688769649593</v>
+        <v>52.08564270111029</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>199.0032048939412</v>
+        <v>194.7512555868483</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>120.1659189998096</v>
+        <v>99.88792016859172</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>12.18348900970292</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.845505757534756</v>
+        <v>2.087195619228719</v>
       </c>
       <c r="C2" t="n">
-        <v>6.180101798233672</v>
+        <v>5.538038799656257</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58127675637212</v>
+        <v>10.6018934581613</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.46114368355552</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C3" t="n">
-        <v>24.06754496961056</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="D3" t="n">
-        <v>49.45063186291184</v>
+        <v>80.12533888210343</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.6147225982413</v>
+        <v>32.55769911593697</v>
       </c>
       <c r="C4" t="n">
-        <v>85.86758120424302</v>
+        <v>82.38335860187109</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2316139805361</v>
+        <v>172.3222475356256</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.01499792413352</v>
+        <v>43.07418052382881</v>
       </c>
       <c r="C5" t="n">
-        <v>165.5717503212246</v>
+        <v>210.46216409791</v>
       </c>
       <c r="D5" t="n">
-        <v>104.7770237357409</v>
+        <v>145.7895340806514</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.10072876957248</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="C6" t="n">
-        <v>228.3878954297525</v>
+        <v>298.2245183713494</v>
       </c>
       <c r="D6" t="n">
-        <v>60.25672884355649</v>
+        <v>71.44668917656163</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>242.4209971142564</v>
+        <v>264.9383624588612</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>180.9164669386022</v>
+        <v>160.5550195525234</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>79.5421807457808</v>
+        <v>64.01093206459626</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.56913593102267</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.698824438974482</v>
+        <v>1.431388152791849</v>
       </c>
       <c r="C2" t="n">
-        <v>2.977640786980576</v>
+        <v>3.379175598017521</v>
       </c>
       <c r="D2" t="n">
-        <v>8.025787482217675</v>
+        <v>9.185231520933158</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.03408343220816</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="C3" t="n">
-        <v>24.53878386764903</v>
+        <v>19.5907754382451</v>
       </c>
       <c r="D3" t="n">
-        <v>47.17297718905924</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.52239725631309</v>
+        <v>29.11176467403067</v>
       </c>
       <c r="C4" t="n">
-        <v>76.10410028550849</v>
+        <v>68.05082386757191</v>
       </c>
       <c r="D4" t="n">
-        <v>110.3975293425538</v>
+        <v>173.2284006666454</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.04645490839843</v>
+        <v>46.60847225911733</v>
       </c>
       <c r="C5" t="n">
-        <v>168.2961002005095</v>
+        <v>196.1777350011189</v>
       </c>
       <c r="D5" t="n">
-        <v>115.9444038715483</v>
+        <v>163.755517068368</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.99634471775284</v>
+        <v>41.62021217383928</v>
       </c>
       <c r="C6" t="n">
-        <v>251.6131008691193</v>
+        <v>324.428346345401</v>
       </c>
       <c r="D6" t="n">
-        <v>70.3196428120863</v>
+        <v>84.85049058264335</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>283.7427579860046</v>
+        <v>323.2679205589812</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>225.227649569782</v>
+        <v>206.0344819517568</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>94.407804483486</v>
+        <v>70.55624400880974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>22.0343454741154</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.81130881880213</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.444952694202058</v>
+        <v>2.66249977391735</v>
       </c>
       <c r="C2" t="n">
-        <v>14.05470013399734</v>
+        <v>10.61956491683775</v>
       </c>
       <c r="D2" t="n">
-        <v>9.05858606708532</v>
+        <v>18.45980208295277</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.6337102953247</v>
+        <v>7.412195167063418</v>
       </c>
       <c r="C3" t="n">
-        <v>18.43231314723387</v>
+        <v>16.71916340332318</v>
       </c>
       <c r="D3" t="n">
-        <v>43.62886797672826</v>
+        <v>65.65928646002668</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.27691927252238</v>
+        <v>24.10877837318892</v>
       </c>
       <c r="C4" t="n">
-        <v>69.19946868154068</v>
+        <v>59.0786315984603</v>
       </c>
       <c r="D4" t="n">
-        <v>107.7428835502704</v>
+        <v>168.4679060487527</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.50020227420971</v>
+        <v>45.40583132141499</v>
       </c>
       <c r="C5" t="n">
-        <v>155.7297295861503</v>
+        <v>166.3816921772282</v>
       </c>
       <c r="D5" t="n">
-        <v>126.277298458746</v>
+        <v>181.5251505152353</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.46177524502383</v>
+        <v>49.22777513404782</v>
       </c>
       <c r="C6" t="n">
-        <v>259.0194055499572</v>
+        <v>323.9050748190375</v>
       </c>
       <c r="D6" t="n">
-        <v>85.49451707662925</v>
+        <v>106.666888066416</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.35117224514665</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="C7" t="n">
-        <v>318.2374453224205</v>
+        <v>379.3217874806571</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76577287597506</v>
+        <v>52.70021676396878</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>288.9823454835699</v>
+        <v>287.3133743863503</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>163.5218611147572</v>
+        <v>134.8999885451457</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>61.06961594267285</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.243915399009714</v>
+        <v>4.93720920465721</v>
       </c>
       <c r="C2" t="n">
-        <v>11.86147576270996</v>
+        <v>10.31816837163398</v>
       </c>
       <c r="D2" t="n">
-        <v>4.476769531365456</v>
+        <v>6.286130550292327</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.439643045053324</v>
+        <v>1.943860454408685</v>
       </c>
       <c r="C2" t="n">
-        <v>7.869689597242432</v>
+        <v>6.202681995431348</v>
       </c>
       <c r="D2" t="n">
-        <v>6.66704865954009</v>
+        <v>13.73366863470863</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.47725255745097</v>
+        <v>10.35252954128262</v>
       </c>
       <c r="C3" t="n">
-        <v>32.43694414831462</v>
+        <v>26.29120351972959</v>
       </c>
       <c r="D3" t="n">
-        <v>47.56567627075796</v>
+        <v>73.17456513603601</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.23108023005904</v>
+        <v>34.12751369502762</v>
       </c>
       <c r="C4" t="n">
-        <v>96.03946916794422</v>
+        <v>88.13934539187015</v>
       </c>
       <c r="D4" t="n">
-        <v>111.3164451937288</v>
+        <v>171.4416198449163</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.22711218151306</v>
+        <v>28.1516154192773</v>
       </c>
       <c r="C5" t="n">
-        <v>225.4092728950677</v>
+        <v>264.1146761349982</v>
       </c>
       <c r="D5" t="n">
-        <v>117.6624623539802</v>
+        <v>163.1910121384261</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.54092728950677</v>
+        <v>15.53713916741002</v>
       </c>
       <c r="C6" t="n">
-        <v>262.9238161697468</v>
+        <v>306.9591276960332</v>
       </c>
       <c r="D6" t="n">
-        <v>70.40014612383455</v>
+        <v>81.38884817746909</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>203.1952675910751</v>
+        <v>202.057422001853</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>120.4997132192535</v>
+        <v>99.38722883942584</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.983572330935061</v>
+        <v>6.572800879932394</v>
       </c>
       <c r="C2" t="n">
-        <v>6.387250563829748</v>
+        <v>6.639559723821178</v>
       </c>
       <c r="D2" t="n">
-        <v>16.46390900021901</v>
+        <v>20.18080580849744</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.26341148437441</v>
+        <v>10.48997421987717</v>
       </c>
       <c r="C3" t="n">
-        <v>29.88930885579414</v>
+        <v>26.00158794697677</v>
       </c>
       <c r="D3" t="n">
-        <v>6.896777622333843</v>
+        <v>8.418486563916399</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39812516635949</v>
+        <v>13.39830389802284</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14312587094085</v>
+        <v>70.14406158376664</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576250019571704</v>
+        <v>1.576271046826217</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.105088062083413</v>
+        <v>4.747731897737575</v>
       </c>
       <c r="C2" t="n">
-        <v>5.934664872171968</v>
+        <v>8.432231031775853</v>
       </c>
       <c r="D2" t="n">
-        <v>16.29995713360979</v>
+        <v>21.88806506618263</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.81934272688536</v>
+        <v>17.78435966243097</v>
       </c>
       <c r="C3" t="n">
-        <v>26.77225989481052</v>
+        <v>25.9328656076795</v>
       </c>
       <c r="D3" t="n">
-        <v>19.05572293943059</v>
+        <v>23.33614292994668</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.41736594749191</v>
+        <v>12.27773678931061</v>
       </c>
       <c r="C4" t="n">
-        <v>46.08618248045802</v>
+        <v>40.15151760828606</v>
       </c>
       <c r="D4" t="n">
-        <v>18.68462230722529</v>
+        <v>19.47591095684822</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="D6" t="n">
         <v>34.3346624606237</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43896575653415</v>
+        <v>15.43965293288006</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13317737855894</v>
+        <v>86.13701109922557</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250308580322979</v>
+        <v>3.25045324902738</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>5.044219704420112</v>
       </c>
       <c r="C2" t="n">
-        <v>8.764061755811277</v>
+        <v>5.65093978564464</v>
       </c>
       <c r="D2" t="n">
-        <v>14.61036933460103</v>
+        <v>34.50057782264141</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.48278319077795</v>
+        <v>17.02841393016093</v>
       </c>
       <c r="C3" t="n">
-        <v>24.55841882173396</v>
+        <v>30.01693605734623</v>
       </c>
       <c r="D3" t="n">
-        <v>27.67055904419635</v>
+        <v>35.43127464626738</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.64329109265569</v>
+        <v>24.83625342203581</v>
       </c>
       <c r="C4" t="n">
-        <v>57.77683414262904</v>
+        <v>54.11393345808419</v>
       </c>
       <c r="D4" t="n">
-        <v>24.03220205225767</v>
+        <v>26.78894960578271</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.37631247036279</v>
+        <v>10.97103059495811</v>
       </c>
       <c r="C5" t="n">
-        <v>50.85453107998479</v>
+        <v>44.59588946541137</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.67332436085985</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.34724525432967</v>
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="D7" t="n">
         <v>37.66867766424586</v>
@@ -5319,7 +5319,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72852604433021</v>
+        <v>16.72947425147706</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0440088704143</v>
+        <v>102.0497929340101</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182131511082551</v>
+        <v>4.182368562869264</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.852198065015236</v>
+        <v>5.255295460833175</v>
       </c>
       <c r="C2" t="n">
-        <v>7.248243300454201</v>
+        <v>11.87718372597791</v>
       </c>
       <c r="D2" t="n">
-        <v>22.1305567491316</v>
+        <v>40.34884889683966</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.43093048890212</v>
+        <v>17.11186248502191</v>
       </c>
       <c r="C3" t="n">
-        <v>30.23782929080176</v>
+        <v>25.39781310886498</v>
       </c>
       <c r="D3" t="n">
-        <v>32.61856747360027</v>
+        <v>53.77032176159781</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.20409001595887</v>
+        <v>28.98413747247858</v>
       </c>
       <c r="C4" t="n">
-        <v>59.2190215201676</v>
+        <v>65.10263551171873</v>
       </c>
       <c r="D4" t="n">
-        <v>32.03442758957343</v>
+        <v>37.87975342065894</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.62423697564751</v>
+        <v>24.07736244665303</v>
       </c>
       <c r="C5" t="n">
-        <v>81.01872929296803</v>
+        <v>74.49010705972675</v>
       </c>
       <c r="D5" t="n">
-        <v>31.1214022246239</v>
+        <v>32.25041208450773</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.87423848286517</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>47.49695393146069</v>
+        <v>42.50574860306991</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.26718391093791</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04835118721363</v>
+        <v>18.04675785864701</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7440053642032</v>
+        <v>117.7336107921258</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016117062404542</v>
+        <v>6.015585952882337</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.718099540160924</v>
+        <v>5.685300955293279</v>
       </c>
       <c r="C2" t="n">
-        <v>4.996114066912019</v>
+        <v>13.02681028765093</v>
       </c>
       <c r="D2" t="n">
-        <v>18.58742928450486</v>
+        <v>32.00202991533328</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94496537529995</v>
+        <v>15.58524480491811</v>
       </c>
       <c r="C3" t="n">
-        <v>27.25331626989146</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D3" t="n">
-        <v>39.68224220565608</v>
+        <v>68.17746932141975</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.41508365691393</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="C4" t="n">
-        <v>56.58990116819465</v>
+        <v>53.66723825265188</v>
       </c>
       <c r="D4" t="n">
-        <v>35.48036203147973</v>
+        <v>48.3068957874643</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.66641106920112</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C5" t="n">
-        <v>71.52032025438015</v>
+        <v>72.64933011426398</v>
       </c>
       <c r="D5" t="n">
-        <v>28.44613973055134</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.16858286768997</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>60.37748381117885</v>
+        <v>55.10451689166923</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>28.50602634051038</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050809690405904</v>
+        <v>7.048162524012438</v>
       </c>
       <c r="C21" t="n">
-        <v>66.98269205885609</v>
+        <v>66.07652366261661</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40675605650369</v>
+        <v>4.405101577507774</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.790347959647687</v>
+        <v>4.231332605303753</v>
       </c>
       <c r="C2" t="n">
-        <v>2.659554530804609</v>
+        <v>7.576147033672636</v>
       </c>
       <c r="D2" t="n">
-        <v>21.28429022807085</v>
+        <v>24.68113728476482</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9014086234146</v>
+        <v>18.10342766631118</v>
       </c>
       <c r="C3" t="n">
-        <v>22.26603793231766</v>
+        <v>44.99349728563132</v>
       </c>
       <c r="D3" t="n">
-        <v>45.70526437121026</v>
+        <v>78.58399498643594</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.71161252132547</v>
+        <v>27.18459393059418</v>
       </c>
       <c r="C4" t="n">
-        <v>64.03056701868123</v>
+        <v>74.41942122502097</v>
       </c>
       <c r="D4" t="n">
-        <v>47.7070479401695</v>
+        <v>72.8240812056199</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.00497515844602</v>
+        <v>28.37250865273283</v>
       </c>
       <c r="C5" t="n">
-        <v>91.86704142489529</v>
+        <v>88.72544877130549</v>
       </c>
       <c r="D5" t="n">
-        <v>35.58835427894688</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.23778823307276</v>
+        <v>20.64909946342317</v>
       </c>
       <c r="C6" t="n">
-        <v>91.8542787047401</v>
+        <v>90.08320584627884</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.97732199181109</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>62.70128062713103</v>
+        <v>56.8323928511436</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>29.95803119509142</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>22.96406055003713</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.270868712156825</v>
+        <v>7.26363452181756</v>
       </c>
       <c r="C21" t="n">
-        <v>76.34412147764667</v>
+        <v>75.36020816385718</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453151534117619</v>
+        <v>5.447725891363169</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.360923302264331</v>
+        <v>3.627557767191965</v>
       </c>
       <c r="C2" t="n">
-        <v>2.392519155249477</v>
+        <v>7.552585088770712</v>
       </c>
       <c r="D2" t="n">
-        <v>16.24007052365074</v>
+        <v>28.34600146471816</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.43016972537612</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="C3" t="n">
-        <v>15.14345833800705</v>
+        <v>35.84360868205105</v>
       </c>
       <c r="D3" t="n">
-        <v>52.1258943569844</v>
+        <v>79.8602670019568</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.09297259892973</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="C4" t="n">
-        <v>58.65746183333842</v>
+        <v>96.15433364934111</v>
       </c>
       <c r="D4" t="n">
-        <v>59.90820840854886</v>
+        <v>93.89533218186919</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.82812170296135</v>
+        <v>35.14656781203582</v>
       </c>
       <c r="C5" t="n">
-        <v>107.0595871481147</v>
+        <v>115.5762484824558</v>
       </c>
       <c r="D5" t="n">
-        <v>44.39953992456201</v>
+        <v>58.29126993965438</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.34095385747668</v>
+        <v>29.78622534684823</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8417623309589</v>
+        <v>116.4077887879528</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>101.0885976108856</v>
+        <v>96.11800898428396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>58.33053984782423</v>
+        <v>53.07328089158257</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47810839064148</v>
+        <v>7.464521808785268</v>
       </c>
       <c r="C21" t="n">
-        <v>85.99824649237701</v>
+        <v>83.97587034883426</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543344841811295</v>
+        <v>6.531456582687109</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_42_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497614224449</v>
+        <v>10.8449762175342</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907127996138</v>
+        <v>37.78907154230666</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.584761778832605</v>
+        <v>5.324017800130453</v>
       </c>
       <c r="C2" t="n">
-        <v>7.061711236647307</v>
+        <v>6.42652047199962</v>
       </c>
       <c r="D2" t="n">
-        <v>36.51021537323463</v>
+        <v>32.30637170364979</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.06844460185679</v>
+        <v>18.24087234490574</v>
       </c>
       <c r="C3" t="n">
-        <v>32.22586839190155</v>
+        <v>34.30226478638355</v>
       </c>
       <c r="D3" t="n">
-        <v>83.27184027421447</v>
+        <v>82.29991004701012</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.84749461513903</v>
+        <v>34.10198825471721</v>
       </c>
       <c r="C4" t="n">
-        <v>92.67011104696917</v>
+        <v>77.21445693901164</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6910719061236</v>
+        <v>108.7639011626871</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.03705403751668</v>
+        <v>43.39324852770903</v>
       </c>
       <c r="C5" t="n">
-        <v>145.3232039211341</v>
+        <v>119.4786956068369</v>
       </c>
       <c r="D5" t="n">
-        <v>75.91364123088462</v>
+        <v>83.08039947188634</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>41.09694064747573</v>
       </c>
       <c r="C6" t="n">
-        <v>149.6154048841012</v>
+        <v>102.0781992967664</v>
       </c>
       <c r="D6" t="n">
-        <v>47.65796055495717</v>
+        <v>52.5284109157256</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>28.50602634051038</v>
       </c>
       <c r="C7" t="n">
-        <v>130.6126963206999</v>
+        <v>71.80404534090746</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>89.45685081096936</v>
+        <v>45.56291095409447</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>46.81562102471339</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.64916522234835</v>
+        <v>7.698115808613853</v>
       </c>
       <c r="C21" t="n">
-        <v>92.74612832097372</v>
+        <v>94.30191865551969</v>
       </c>
       <c r="D21" t="n">
-        <v>7.64916522234835</v>
+        <v>8.660380284690584</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.201299337099601</v>
+        <v>6.110397711232148</v>
       </c>
       <c r="C2" t="n">
-        <v>5.795256698168921</v>
+        <v>6.606180301876787</v>
       </c>
       <c r="D2" t="n">
-        <v>32.1031499288707</v>
+        <v>35.80237527847268</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.46114368355552</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="C3" t="n">
-        <v>29.66841562233861</v>
+        <v>29.31498644880976</v>
       </c>
       <c r="D3" t="n">
-        <v>90.51222959303469</v>
+        <v>87.54244278768809</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.44810322595982</v>
+        <v>34.395530818287</v>
       </c>
       <c r="C4" t="n">
-        <v>85.84205576393261</v>
+        <v>80.60934050029711</v>
       </c>
       <c r="D4" t="n">
-        <v>123.568656542729</v>
+        <v>122.6242152512436</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.07418052382881</v>
+        <v>46.80482179996669</v>
       </c>
       <c r="C5" t="n">
-        <v>156.8096520608218</v>
+        <v>130.6215320500382</v>
       </c>
       <c r="D5" t="n">
-        <v>92.57880851047423</v>
+        <v>99.10743074371554</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.8466360406218</v>
+        <v>49.1875234781737</v>
       </c>
       <c r="C6" t="n">
-        <v>184.2318289358437</v>
+        <v>142.4103584826338</v>
       </c>
       <c r="D6" t="n">
-        <v>57.60011955586462</v>
+        <v>64.6844109897096</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.19525428662065</v>
+        <v>38.26754376383641</v>
       </c>
       <c r="C7" t="n">
-        <v>169.2994463542497</v>
+        <v>107.8557845362588</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.69385894719101</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="C8" t="n">
-        <v>125.6735236206342</v>
+        <v>68.59471209572465</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.816576125314478</v>
+        <v>7.879405199954857</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6384176134239</v>
+        <v>102.4322675994132</v>
       </c>
       <c r="D21" t="n">
-        <v>8.793648140978787</v>
+        <v>9.849256499943571</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.346017160251383</v>
+        <v>8.897579443588842</v>
       </c>
       <c r="C2" t="n">
-        <v>10.70399521940297</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D2" t="n">
-        <v>30.56278778090745</v>
+        <v>31.3648756552771</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4968875115359</v>
+        <v>18.77101610519901</v>
       </c>
       <c r="C3" t="n">
-        <v>26.19793748782614</v>
+        <v>27.35149104031614</v>
       </c>
       <c r="D3" t="n">
-        <v>93.9876164660684</v>
+        <v>93.50656009098746</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>33.56595400819845</v>
       </c>
       <c r="C4" t="n">
-        <v>80.4561878584346</v>
+        <v>76.98472797621788</v>
       </c>
       <c r="D4" t="n">
-        <v>133.6384427451886</v>
+        <v>135.0168165219511</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.5096755938869</v>
+        <v>48.52288028239862</v>
       </c>
       <c r="C5" t="n">
-        <v>155.2879431192393</v>
+        <v>136.9538047424301</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3604028562417</v>
+        <v>114.8153940116645</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.31456984264904</v>
+        <v>55.50703345041042</v>
       </c>
       <c r="C6" t="n">
-        <v>208.8658423308047</v>
+        <v>169.3387162624196</v>
       </c>
       <c r="D6" t="n">
-        <v>69.51460969460392</v>
+        <v>77.88695411642071</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.9206269713388</v>
+        <v>46.65166915810418</v>
       </c>
       <c r="C7" t="n">
-        <v>209.2438151969397</v>
+        <v>150.6148240470244</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>51.56237117474672</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.36974333606933</v>
+        <v>30.12492830481337</v>
       </c>
       <c r="C8" t="n">
-        <v>164.3102045212674</v>
+        <v>99.88792016859172</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>41.97462309507237</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>106.3890534661141</v>
+        <v>61.4593697812588</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.96795429162639</v>
+        <v>8.044609265425931</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5673829369563</v>
+        <v>110.6133773996065</v>
       </c>
       <c r="D21" t="n">
-        <v>9.959942864532987</v>
+        <v>11.06133773996065</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.821763886183585</v>
+        <v>7.9256492163845</v>
       </c>
       <c r="C2" t="n">
-        <v>7.534913630094269</v>
+        <v>7.313038648934491</v>
       </c>
       <c r="D2" t="n">
-        <v>25.35167096676538</v>
+        <v>25.80916539694439</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.41758693167016</v>
+        <v>22.9925312334603</v>
       </c>
       <c r="C3" t="n">
-        <v>43.65341166933442</v>
+        <v>44.6449768506237</v>
       </c>
       <c r="D3" t="n">
-        <v>101.9986777327224</v>
+        <v>102.1263049342745</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.42035224833366</v>
+        <v>23.30472700341079</v>
       </c>
       <c r="C4" t="n">
-        <v>119.9950948992706</v>
+        <v>111.2271061526424</v>
       </c>
       <c r="D4" t="n">
-        <v>125.4320136853895</v>
+        <v>129.4012196536594</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.34796496012666</v>
+        <v>31.26866438026092</v>
       </c>
       <c r="C5" t="n">
-        <v>124.8046769023758</v>
+        <v>101.1691009226338</v>
       </c>
       <c r="D5" t="n">
-        <v>69.60591223109887</v>
+        <v>77.38626278725484</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.00256969468102</v>
+        <v>28.94094057349173</v>
       </c>
       <c r="C6" t="n">
-        <v>137.8216697129843</v>
+        <v>99.18008007382979</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>115.5212706110179</v>
+        <v>70.24699348197203</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>78.35819301445918</v>
+        <v>45.22911673465055</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.495021827118645</v>
+        <v>4.765403356414017</v>
       </c>
       <c r="C2" t="n">
-        <v>3.355613653115598</v>
+        <v>3.262347621212151</v>
       </c>
       <c r="D2" t="n">
-        <v>18.42740440871263</v>
+        <v>18.92416874706152</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.74785507092459</v>
+        <v>25.60888886527805</v>
       </c>
       <c r="C3" t="n">
-        <v>37.394770054761</v>
+        <v>37.06588457383832</v>
       </c>
       <c r="D3" t="n">
-        <v>99.45595117872313</v>
+        <v>99.90264638415543</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.44435616159208</v>
+        <v>32.20034295159113</v>
       </c>
       <c r="C4" t="n">
-        <v>118.0806868759894</v>
+        <v>115.4643292441716</v>
       </c>
       <c r="D4" t="n">
-        <v>144.1421614329252</v>
+        <v>148.8516051701972</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>34.38571334124454</v>
       </c>
       <c r="C5" t="n">
-        <v>169.8914402199105</v>
+        <v>150.4528356758237</v>
       </c>
       <c r="D5" t="n">
-        <v>88.57818661566847</v>
+        <v>97.90478980601318</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.5510068084565</v>
+        <v>34.73717901936489</v>
       </c>
       <c r="C6" t="n">
-        <v>166.7223586306019</v>
+        <v>127.3159875298391</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20511282139213</v>
+        <v>43.43153668817465</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>148.4589060884984</v>
+        <v>97.61517423326035</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54217107911827</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>101.8906854852552</v>
+        <v>60.4167537193487</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>49.81093327037041</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.270201602846125</v>
+        <v>5.593998418798326</v>
       </c>
       <c r="C2" t="n">
-        <v>5.21406205725481</v>
+        <v>3.675663404700058</v>
       </c>
       <c r="D2" t="n">
-        <v>17.08830054011998</v>
+        <v>24.20498964820511</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.82577299245858</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01493150420873</v>
+        <v>24.21971586376881</v>
       </c>
       <c r="D3" t="n">
-        <v>92.73097940463248</v>
+        <v>93.22676199527712</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>39.98560224626834</v>
       </c>
       <c r="C4" t="n">
-        <v>105.8029500866787</v>
+        <v>103.7098639812246</v>
       </c>
       <c r="D4" t="n">
-        <v>155.9476775764931</v>
+        <v>162.4183766951838</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>40.88979188187966</v>
       </c>
       <c r="C5" t="n">
-        <v>192.152569413707</v>
+        <v>180.9851892778995</v>
       </c>
       <c r="D5" t="n">
-        <v>114.8399377042707</v>
+        <v>123.8474728907351</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="C6" t="n">
-        <v>215.1048489912932</v>
+        <v>181.1727030894106</v>
       </c>
       <c r="D6" t="n">
-        <v>53.93721887131977</v>
+        <v>59.69320566131882</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>190.7987393295506</v>
+        <v>138.0985225655818</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>142.9473744768568</v>
+        <v>91.29271901791088</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>80.42968067041991</v>
+        <v>53.0281204971872</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>36.72718161587318</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.980185119465816</v>
+        <v>3.290818304635308</v>
       </c>
       <c r="C2" t="n">
-        <v>2.564325003492669</v>
+        <v>1.769109363052752</v>
       </c>
       <c r="D2" t="n">
-        <v>11.93412509282423</v>
+        <v>16.87133429748144</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.39380400258999</v>
+        <v>22.10404956111694</v>
       </c>
       <c r="C3" t="n">
-        <v>24.67131980772234</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="D3" t="n">
-        <v>89.89372853935919</v>
+        <v>94.02688637423826</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.86775146402972</v>
+        <v>44.05690997577986</v>
       </c>
       <c r="C4" t="n">
-        <v>101.2338962711141</v>
+        <v>98.20913159432968</v>
       </c>
       <c r="D4" t="n">
-        <v>167.1916340332318</v>
+        <v>172.7944681813683</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.57010198319369</v>
+        <v>43.02509313861647</v>
       </c>
       <c r="C5" t="n">
-        <v>226.9800692218626</v>
+        <v>213.6528441367122</v>
       </c>
       <c r="D5" t="n">
-        <v>120.5340743889022</v>
+        <v>130.6215320500382</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.53842401475054</v>
+        <v>33.61013265488955</v>
       </c>
       <c r="C6" t="n">
-        <v>247.8294452169521</v>
+        <v>210.2343986305247</v>
       </c>
       <c r="D6" t="n">
-        <v>52.08564270111029</v>
+        <v>58.04288777047993</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>194.7512555868483</v>
+        <v>136.3019242668101</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>99.88792016859172</v>
+        <v>66.7588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.087195619228719</v>
+        <v>3.374266859496287</v>
       </c>
       <c r="C2" t="n">
-        <v>5.538038799656257</v>
+        <v>1.716094987023425</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6018934581613</v>
+        <v>22.83839684389355</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.21646752101981</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="C3" t="n">
-        <v>17.47510913559323</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="D3" t="n">
-        <v>80.12533888210343</v>
+        <v>87.29209712310515</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>43.48258756879548</v>
       </c>
       <c r="C4" t="n">
-        <v>82.38335860187109</v>
+        <v>77.22721965916685</v>
       </c>
       <c r="D4" t="n">
-        <v>172.3222475356256</v>
+        <v>178.5504549713674</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.07418052382881</v>
+        <v>52.69530802544756</v>
       </c>
       <c r="C5" t="n">
-        <v>210.46216409791</v>
+        <v>200.3010753589555</v>
       </c>
       <c r="D5" t="n">
-        <v>145.7895340806514</v>
+        <v>155.680642200938</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>42.86801350593698</v>
       </c>
       <c r="C6" t="n">
-        <v>298.2245183713494</v>
+        <v>268.2370347451306</v>
       </c>
       <c r="D6" t="n">
-        <v>71.44668917656163</v>
+        <v>78.24921901928779</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>264.9383624588612</v>
+        <v>206.7285775786594</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>160.5550195525234</v>
+        <v>113.3231375012093</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>47.48124596819272</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.431388152791849</v>
+        <v>2.303180114163017</v>
       </c>
       <c r="C2" t="n">
-        <v>3.379175598017521</v>
+        <v>2.021418523044182</v>
       </c>
       <c r="D2" t="n">
-        <v>9.185231520933158</v>
+        <v>15.93376523992573</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.621127501618743</v>
+        <v>14.7900291644782</v>
       </c>
       <c r="C3" t="n">
-        <v>19.5907754382451</v>
+        <v>10.85322087044849</v>
       </c>
       <c r="D3" t="n">
-        <v>72.8554971321558</v>
+        <v>86.60487373013238</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.11176467403067</v>
+        <v>40.11322944782042</v>
       </c>
       <c r="C4" t="n">
-        <v>68.05082386757191</v>
+        <v>61.4524975473291</v>
       </c>
       <c r="D4" t="n">
-        <v>173.2284006666454</v>
+        <v>180.8732700396153</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.60847225911733</v>
+        <v>58.51216317310991</v>
       </c>
       <c r="C5" t="n">
-        <v>196.1777350011189</v>
+        <v>185.4275976396163</v>
       </c>
       <c r="D5" t="n">
-        <v>163.755517068368</v>
+        <v>172.2476347101029</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.62021217383928</v>
+        <v>50.11331156327844</v>
       </c>
       <c r="C6" t="n">
-        <v>324.428346345401</v>
+        <v>297.5402402214894</v>
       </c>
       <c r="D6" t="n">
-        <v>84.85049058264335</v>
+        <v>94.87315289529903</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>323.2679205589812</v>
+        <v>264.0400633094754</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>47.49008169753095</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>206.0344819517568</v>
+        <v>153.4618923893402</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>55.02499532762521</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.66249977391735</v>
+        <v>3.565707661824415</v>
       </c>
       <c r="C2" t="n">
-        <v>10.61956491683775</v>
+        <v>10.79137076508094</v>
       </c>
       <c r="D2" t="n">
-        <v>18.45980208295277</v>
+        <v>29.38763577892402</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.412195167063418</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C3" t="n">
-        <v>16.71916340332318</v>
+        <v>9.390416791120741</v>
       </c>
       <c r="D3" t="n">
-        <v>65.65928646002668</v>
+        <v>80.22842239104935</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.10877837318892</v>
+        <v>34.68907338185679</v>
       </c>
       <c r="C4" t="n">
-        <v>59.0786315984603</v>
+        <v>46.12447064092365</v>
       </c>
       <c r="D4" t="n">
-        <v>168.4679060487527</v>
+        <v>181.7411350101695</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.40583132141499</v>
+        <v>58.97849333262715</v>
       </c>
       <c r="C5" t="n">
-        <v>166.3816921772282</v>
+        <v>154.4534575706295</v>
       </c>
       <c r="D5" t="n">
-        <v>181.5251505152353</v>
+        <v>190.6063167795183</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.22777513404782</v>
+        <v>60.82025202579416</v>
       </c>
       <c r="C6" t="n">
-        <v>323.9050748190375</v>
+        <v>297.5402402214894</v>
       </c>
       <c r="D6" t="n">
-        <v>106.666888066416</v>
+        <v>117.0518152819387</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>31.02126395879071</v>
       </c>
       <c r="C7" t="n">
-        <v>379.3217874806571</v>
+        <v>333.0294379823072</v>
       </c>
       <c r="D7" t="n">
-        <v>52.70021676396878</v>
+        <v>57.97023844036566</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>287.3133743863503</v>
+        <v>226.8966206670016</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>134.8999885451457</v>
+        <v>103.6156162016168</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.93720920465721</v>
+        <v>4.674100819919064</v>
       </c>
       <c r="C2" t="n">
-        <v>10.31816837163398</v>
+        <v>2.634029090494193</v>
       </c>
       <c r="D2" t="n">
-        <v>6.286130550292327</v>
+        <v>15.85031668506475</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.943860454408685</v>
+        <v>2.580032966760618</v>
       </c>
       <c r="C2" t="n">
-        <v>6.202681995431348</v>
+        <v>6.215444715586557</v>
       </c>
       <c r="D2" t="n">
-        <v>13.73366863470863</v>
+        <v>21.86352137357647</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.35252954128262</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="C3" t="n">
-        <v>26.29120351972959</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="D3" t="n">
-        <v>73.17456513603601</v>
+        <v>89.94281592457153</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.12751369502762</v>
+        <v>46.08618248045802</v>
       </c>
       <c r="C4" t="n">
-        <v>88.13934539187015</v>
+        <v>72.05831799630738</v>
       </c>
       <c r="D4" t="n">
-        <v>171.4416198449163</v>
+        <v>186.0421717024748</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.1516154192773</v>
+        <v>35.34291735288518</v>
       </c>
       <c r="C5" t="n">
-        <v>264.1146761349982</v>
+        <v>243.3507121901782</v>
       </c>
       <c r="D5" t="n">
-        <v>163.1910121384261</v>
+        <v>172.1985473248906</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.53713916741002</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="C6" t="n">
-        <v>306.9591276960332</v>
+        <v>274.7578029967379</v>
       </c>
       <c r="D6" t="n">
-        <v>81.38884817746909</v>
+        <v>90.56622571676827</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>202.057422001853</v>
+        <v>159.5379289309237</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>99.38722883942584</v>
+        <v>76.35542769779568</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.572800879932394</v>
+        <v>7.015569094547707</v>
       </c>
       <c r="C2" t="n">
-        <v>6.639559723821178</v>
+        <v>5.072690387843269</v>
       </c>
       <c r="D2" t="n">
-        <v>20.18080580849744</v>
+        <v>19.30115986549229</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.48997421987717</v>
+        <v>9.935286766977722</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00158794697677</v>
+        <v>6.636614480708438</v>
       </c>
       <c r="D3" t="n">
-        <v>8.418486563916399</v>
+        <v>16.44918278465531</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39830389802284</v>
+        <v>13.39802622383029</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14406158376664</v>
+        <v>70.14260787769973</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576271046826217</v>
+        <v>1.576238379274151</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.747731897737575</v>
+        <v>5.114905539125882</v>
       </c>
       <c r="C2" t="n">
-        <v>8.432231031775853</v>
+        <v>4.286310476741575</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88806506618263</v>
+        <v>21.74276640595411</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.78435966243097</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9328656076795</v>
+        <v>14.85875150377547</v>
       </c>
       <c r="D3" t="n">
-        <v>23.33614292994668</v>
+        <v>28.6866679180918</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.27773678931061</v>
+        <v>11.65236350170539</v>
       </c>
       <c r="C4" t="n">
-        <v>40.15151760828606</v>
+        <v>10.66963404975434</v>
       </c>
       <c r="D4" t="n">
-        <v>19.47591095684822</v>
+        <v>23.68760860806704</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43965293288006</v>
+        <v>15.44202005236402</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13701109922557</v>
+        <v>86.15021713424139</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25045324902738</v>
+        <v>3.250951589971373</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.044219704420112</v>
+        <v>4.583780031128358</v>
       </c>
       <c r="C2" t="n">
-        <v>5.65093978564464</v>
+        <v>4.726133448244146</v>
       </c>
       <c r="D2" t="n">
-        <v>34.50057782264141</v>
+        <v>33.09766035327272</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02841393016093</v>
+        <v>18.04452280405637</v>
       </c>
       <c r="C3" t="n">
-        <v>30.01693605734623</v>
+        <v>15.96321767105314</v>
       </c>
       <c r="D3" t="n">
-        <v>35.43127464626738</v>
+        <v>39.42207906403067</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.83625342203581</v>
+        <v>25.19360958638165</v>
       </c>
       <c r="C4" t="n">
-        <v>54.11393345808419</v>
+        <v>26.27844079957437</v>
       </c>
       <c r="D4" t="n">
-        <v>26.78894960578271</v>
+        <v>32.73637719810989</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.97103059495811</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="C5" t="n">
-        <v>44.59588946541137</v>
+        <v>13.49903093339365</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>30.92505268377453</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72947425147706</v>
+        <v>16.73878723431325</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0497929340101</v>
+        <v>102.1066021293108</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182368562869264</v>
+        <v>5.021636170293975</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.255295460833175</v>
+        <v>5.15221195188726</v>
       </c>
       <c r="C2" t="n">
-        <v>11.87718372597791</v>
+        <v>11.1408729477928</v>
       </c>
       <c r="D2" t="n">
-        <v>40.34884889683966</v>
+        <v>32.87676711981719</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.11186248502191</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C3" t="n">
-        <v>25.39781310886498</v>
+        <v>17.5143790437631</v>
       </c>
       <c r="D3" t="n">
-        <v>53.77032176159781</v>
+        <v>55.80744824790993</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.98413747247858</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="C4" t="n">
-        <v>65.10263551171873</v>
+        <v>33.65529304928491</v>
       </c>
       <c r="D4" t="n">
-        <v>37.87975342065894</v>
+        <v>44.14624901686633</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.07736244665303</v>
+        <v>24.51914891356409</v>
       </c>
       <c r="C5" t="n">
-        <v>74.49010705972675</v>
+        <v>32.7658296292373</v>
       </c>
       <c r="D5" t="n">
-        <v>32.25041208450773</v>
+        <v>35.80924751240241</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.30442390377452</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>42.50574860306991</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04675785864701</v>
+        <v>18.06908677064635</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7336107921258</v>
+        <v>117.8792803608834</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015585952882337</v>
+        <v>6.883461626912896</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.685300955293279</v>
+        <v>6.183047041346412</v>
       </c>
       <c r="C2" t="n">
-        <v>13.02681028765093</v>
+        <v>10.38394546781851</v>
       </c>
       <c r="D2" t="n">
-        <v>32.00202991533328</v>
+        <v>27.48206348498096</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.58524480491811</v>
+        <v>15.44780012632356</v>
       </c>
       <c r="C3" t="n">
-        <v>34.77841242294325</v>
+        <v>30.62071089545801</v>
       </c>
       <c r="D3" t="n">
-        <v>68.17746932141975</v>
+        <v>64.32901832077225</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.50067563363265</v>
+        <v>23.11328620108265</v>
       </c>
       <c r="C4" t="n">
-        <v>53.66723825265188</v>
+        <v>33.06820792214531</v>
       </c>
       <c r="D4" t="n">
-        <v>48.3068957874643</v>
+        <v>53.06739040535709</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.69033286700153</v>
+        <v>21.52481841561132</v>
       </c>
       <c r="C5" t="n">
-        <v>72.64933011426398</v>
+        <v>36.32466505713199</v>
       </c>
       <c r="D5" t="n">
-        <v>30.99868376159304</v>
+        <v>35.39200473809752</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.47172192412398</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>55.10451689166923</v>
+        <v>23.82898027747859</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>31.71830482880595</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>26.35010838198439</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048162524012438</v>
+        <v>7.064166003730895</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07652366261661</v>
+        <v>66.22655628497714</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405101577507774</v>
+        <v>5.298124502798172</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.231332605303753</v>
+        <v>4.765403356414017</v>
       </c>
       <c r="C2" t="n">
-        <v>7.576147033672636</v>
+        <v>6.505060288339365</v>
       </c>
       <c r="D2" t="n">
-        <v>24.68113728476482</v>
+        <v>21.87922933684441</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.10342766631118</v>
+        <v>19.29134238844982</v>
       </c>
       <c r="C3" t="n">
-        <v>44.99349728563132</v>
+        <v>37.16405934426301</v>
       </c>
       <c r="D3" t="n">
-        <v>78.58399498643594</v>
+        <v>72.34989706446869</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.18459393059418</v>
+        <v>27.58023825540564</v>
       </c>
       <c r="C4" t="n">
-        <v>74.41942122502097</v>
+        <v>60.96751418143117</v>
       </c>
       <c r="D4" t="n">
-        <v>72.8240812056199</v>
+        <v>75.56806603898974</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.37250865273283</v>
+        <v>29.62423697564751</v>
       </c>
       <c r="C5" t="n">
-        <v>88.72544877130549</v>
+        <v>51.78719139901926</v>
       </c>
       <c r="D5" t="n">
-        <v>41.62610266006477</v>
+        <v>47.73748211900116</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.64909946342317</v>
+        <v>22.05790741901734</v>
       </c>
       <c r="C6" t="n">
-        <v>90.08320584627884</v>
+        <v>44.11581483803468</v>
       </c>
       <c r="D6" t="n">
-        <v>33.85164259013428</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>56.8323928511436</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>28.03871443328891</v>
+        <v>19.69385894719101</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96406055003713</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26363452181756</v>
+        <v>7.288784675082328</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36020816385718</v>
+        <v>75.62114100397915</v>
       </c>
       <c r="D21" t="n">
-        <v>5.447725891363169</v>
+        <v>6.377686590697037</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.627557767191965</v>
+        <v>5.477170441992955</v>
       </c>
       <c r="C2" t="n">
-        <v>7.552585088770712</v>
+        <v>9.725192758268904</v>
       </c>
       <c r="D2" t="n">
-        <v>28.34600146471816</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12520604225386</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="C3" t="n">
-        <v>35.84360868205105</v>
+        <v>29.87949137875168</v>
       </c>
       <c r="D3" t="n">
-        <v>79.8602670019568</v>
+        <v>73.06657288856887</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>33.57871672835365</v>
       </c>
       <c r="C4" t="n">
-        <v>96.15433364934111</v>
+        <v>80.22645889564085</v>
       </c>
       <c r="D4" t="n">
-        <v>93.89533218186919</v>
+        <v>94.15058658497337</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.14656781203582</v>
+        <v>36.47192721276901</v>
       </c>
       <c r="C5" t="n">
-        <v>115.5762484824558</v>
+        <v>87.1546524445106</v>
       </c>
       <c r="D5" t="n">
-        <v>58.29126993965438</v>
+        <v>65.01624171374503</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.78622534684823</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="C6" t="n">
-        <v>116.4077887879528</v>
+        <v>65.52969576306612</v>
       </c>
       <c r="D6" t="n">
-        <v>38.96360288614742</v>
+        <v>43.19002675292993</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>96.11800898428396</v>
+        <v>47.19064864773568</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>53.07328089158257</v>
+        <v>28.28906009787184</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.73906039931537</v>
       </c>
       <c r="D9" t="n">
         <v>32.39374724932775</v>
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.464521808785268</v>
+        <v>7.501179896962925</v>
       </c>
       <c r="C21" t="n">
-        <v>83.97587034883426</v>
+        <v>85.32592132795327</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531456582687109</v>
+        <v>7.501179896962925</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_42_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762175342</v>
+        <v>10.84497639647253</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907154230666</v>
+        <v>37.78907216581317</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.324017800130453</v>
+        <v>1.20656792851933</v>
       </c>
       <c r="C2" t="n">
-        <v>6.42652047199962</v>
+        <v>3.09643225919444</v>
       </c>
       <c r="D2" t="n">
-        <v>32.30637170364979</v>
+        <v>18.88686233430014</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24087234490574</v>
+        <v>11.45208697003904</v>
       </c>
       <c r="C3" t="n">
-        <v>34.30226478638355</v>
+        <v>36.12340677776139</v>
       </c>
       <c r="D3" t="n">
-        <v>82.29991004701012</v>
+        <v>71.12271243416018</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.10198825471721</v>
+        <v>19.68011447933156</v>
       </c>
       <c r="C4" t="n">
-        <v>77.21445693901164</v>
+        <v>96.26919813073798</v>
       </c>
       <c r="D4" t="n">
-        <v>108.7639011626871</v>
+        <v>78.6566443165502</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.39324852770903</v>
+        <v>17.42602175038089</v>
       </c>
       <c r="C5" t="n">
-        <v>119.4786956068369</v>
+        <v>94.81228453763572</v>
       </c>
       <c r="D5" t="n">
-        <v>83.08039947188634</v>
+        <v>51.0999680060465</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.09694064747573</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>102.0781992967664</v>
+        <v>59.93471559656354</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5284109157256</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.50602634051038</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>71.80404534090746</v>
+        <v>33.95570784678443</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>45.56291095409447</v>
+        <v>28.28906009787184</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>30.61874740004951</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.698115808613853</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.30191865551969</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.660380284690584</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.110397711232148</v>
+        <v>1.351866588747858</v>
       </c>
       <c r="C2" t="n">
-        <v>6.606180301876787</v>
+        <v>10.20526738564559</v>
       </c>
       <c r="D2" t="n">
-        <v>35.80237527847268</v>
+        <v>18.22614612934203</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95616551067416</v>
+        <v>7.485826244881929</v>
       </c>
       <c r="C3" t="n">
-        <v>29.31498644880976</v>
+        <v>21.74571164906685</v>
       </c>
       <c r="D3" t="n">
-        <v>87.54244278768809</v>
+        <v>70.41094534858125</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.395530818287</v>
+        <v>21.30097993904305</v>
       </c>
       <c r="C4" t="n">
-        <v>80.60934050029711</v>
+        <v>93.88256946171398</v>
       </c>
       <c r="D4" t="n">
-        <v>122.6242152512436</v>
+        <v>95.64382484313276</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.80482179996669</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="C5" t="n">
-        <v>130.6215320500382</v>
+        <v>141.4207567967531</v>
       </c>
       <c r="D5" t="n">
-        <v>99.10743074371554</v>
+        <v>66.83247496660162</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.1875234781737</v>
+        <v>18.15349679922777</v>
       </c>
       <c r="C6" t="n">
-        <v>142.4103584826338</v>
+        <v>106.9889013134089</v>
       </c>
       <c r="D6" t="n">
-        <v>64.6844109897096</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.26754376383641</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>107.8557845362588</v>
+        <v>61.32388859807276</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>68.59471209572465</v>
+        <v>37.55184968744049</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.879405199954857</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.4322675994132</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.849256499943571</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.897579443588842</v>
+        <v>0.7088218424661971</v>
       </c>
       <c r="C2" t="n">
-        <v>10.75504610002381</v>
+        <v>4.191080949429634</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3648756552771</v>
+        <v>12.31406145436774</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.77101610519901</v>
+        <v>6.994952392758524</v>
       </c>
       <c r="C3" t="n">
-        <v>27.35149104031614</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D3" t="n">
-        <v>93.50656009098746</v>
+        <v>71.14725612676635</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.56595400819845</v>
+        <v>23.16433708170349</v>
       </c>
       <c r="C4" t="n">
-        <v>76.98472797621788</v>
+        <v>86.23770008874408</v>
       </c>
       <c r="D4" t="n">
-        <v>135.0168165219511</v>
+        <v>107.3982901060798</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.52288028239862</v>
+        <v>23.80738182798515</v>
       </c>
       <c r="C5" t="n">
-        <v>136.9538047424301</v>
+        <v>169.7196343716674</v>
       </c>
       <c r="D5" t="n">
-        <v>114.8153940116645</v>
+        <v>76.79721416470676</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.50703345041042</v>
+        <v>14.6516027381794</v>
       </c>
       <c r="C6" t="n">
-        <v>169.3387162624196</v>
+        <v>142.450610138508</v>
       </c>
       <c r="D6" t="n">
-        <v>77.88695411642071</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.65166915810418</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>150.6148240470244</v>
+        <v>60.48547605864599</v>
       </c>
       <c r="D7" t="n">
-        <v>51.56237117474672</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.12492830481337</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>99.88792016859172</v>
+        <v>39.22082078466007</v>
       </c>
       <c r="D8" t="n">
-        <v>41.97462309507237</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>61.4593697812588</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>40.57072387799944</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.82848155585983</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.044609265425931</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.6133773996065</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06133773996065</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.9256492163845</v>
+        <v>0.5959208564778139</v>
       </c>
       <c r="C2" t="n">
-        <v>7.313038648934491</v>
+        <v>4.316744655573225</v>
       </c>
       <c r="D2" t="n">
-        <v>25.80916539694439</v>
+        <v>11.13007372304609</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.9925312334603</v>
+        <v>4.638757902566179</v>
       </c>
       <c r="C3" t="n">
-        <v>44.6449768506237</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D3" t="n">
-        <v>102.1263049342745</v>
+        <v>64.6824474943011</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.30472700341079</v>
+        <v>18.45489334443154</v>
       </c>
       <c r="C4" t="n">
-        <v>111.2271061526424</v>
+        <v>84.09356310266904</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4012196536594</v>
+        <v>119.3059080108894</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.26866438026092</v>
+        <v>29.62423697564751</v>
       </c>
       <c r="C5" t="n">
-        <v>101.1691009226338</v>
+        <v>165.8662746324986</v>
       </c>
       <c r="D5" t="n">
-        <v>77.38626278725484</v>
+        <v>95.62222639363934</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94094057349173</v>
+        <v>22.29941735426205</v>
       </c>
       <c r="C6" t="n">
-        <v>99.18008007382979</v>
+        <v>206.2897363548611</v>
       </c>
       <c r="D6" t="n">
-        <v>33.93214590188251</v>
+        <v>51.76362945411734</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>70.24699348197203</v>
+        <v>129.8940570011912</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>45.22911673465055</v>
+        <v>58.83123117699011</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.765403356414017</v>
+        <v>0.4771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>3.262347621212151</v>
+        <v>2.492657421082652</v>
       </c>
       <c r="D2" t="n">
-        <v>18.92416874706152</v>
+        <v>8.442048508818322</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.60888886527805</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C3" t="n">
-        <v>37.06588457383832</v>
+        <v>20.23382018452676</v>
       </c>
       <c r="D3" t="n">
-        <v>99.90264638415543</v>
+        <v>59.72462158785471</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.20034295159113</v>
+        <v>15.00895890252524</v>
       </c>
       <c r="C4" t="n">
-        <v>115.4643292441716</v>
+        <v>73.75575977695013</v>
       </c>
       <c r="D4" t="n">
-        <v>148.8516051701972</v>
+        <v>124.3216570318863</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.38571334124454</v>
+        <v>30.90050899116836</v>
       </c>
       <c r="C5" t="n">
-        <v>150.4528356758237</v>
+        <v>167.0198281849886</v>
       </c>
       <c r="D5" t="n">
-        <v>97.90478980601318</v>
+        <v>112.5328305992907</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.73717901936489</v>
+        <v>27.85414586489051</v>
       </c>
       <c r="C6" t="n">
-        <v>127.3159875298391</v>
+        <v>240.7451537831071</v>
       </c>
       <c r="D6" t="n">
-        <v>43.43153668817465</v>
+        <v>63.71837124873075</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>97.61517423326035</v>
+        <v>190.7388527195915</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>60.4167537193487</v>
+        <v>89.12305659152544</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>47.7031209493525</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.593998418798326</v>
+        <v>0.7736171909464865</v>
       </c>
       <c r="C2" t="n">
-        <v>3.675663404700058</v>
+        <v>13.33998780530566</v>
       </c>
       <c r="D2" t="n">
-        <v>24.20498964820511</v>
+        <v>12.61840324268425</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.06830573313655</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C3" t="n">
-        <v>24.21971586376881</v>
+        <v>14.79493790299943</v>
       </c>
       <c r="D3" t="n">
-        <v>93.22676199527712</v>
+        <v>53.32853529468674</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.98560224626834</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C4" t="n">
-        <v>103.7098639812246</v>
+        <v>62.06510811477911</v>
       </c>
       <c r="D4" t="n">
-        <v>162.4183766951838</v>
+        <v>125.585166327252</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.88979188187966</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="C5" t="n">
-        <v>180.9851892778995</v>
+        <v>151.9254572321939</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8474728907351</v>
+        <v>128.5353181785137</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="C6" t="n">
-        <v>181.1727030894106</v>
+        <v>255.4370081771607</v>
       </c>
       <c r="D6" t="n">
-        <v>59.69320566131882</v>
+        <v>80.26180181299375</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>19.46314823669301</v>
       </c>
       <c r="C7" t="n">
-        <v>138.0985225655818</v>
+        <v>261.1655060314407</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>91.29271901791088</v>
+        <v>160.8888137719673</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>74.43905617910588</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>36.72718161587318</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.290818304635308</v>
+        <v>0.5193445355465627</v>
       </c>
       <c r="C2" t="n">
-        <v>1.769109363052752</v>
+        <v>6.936047530503715</v>
       </c>
       <c r="D2" t="n">
-        <v>16.87133429748144</v>
+        <v>9.086075002804231</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.10404956111694</v>
+        <v>3.863177216211199</v>
       </c>
       <c r="C3" t="n">
-        <v>21.51990967709008</v>
+        <v>30.46363126277852</v>
       </c>
       <c r="D3" t="n">
-        <v>94.02688637423826</v>
+        <v>58.56125055832224</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.05690997577986</v>
+        <v>18.71014774753571</v>
       </c>
       <c r="C4" t="n">
-        <v>98.20913159432968</v>
+        <v>86.32703912983054</v>
       </c>
       <c r="D4" t="n">
-        <v>172.7944681813683</v>
+        <v>129.2863551722625</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.02509313861647</v>
+        <v>21.00940087088174</v>
       </c>
       <c r="C5" t="n">
-        <v>213.6528441367122</v>
+        <v>220.9423208407447</v>
       </c>
       <c r="D5" t="n">
-        <v>130.6215320500382</v>
+        <v>118.0306177430728</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.61013265488955</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="C6" t="n">
-        <v>210.2343986305247</v>
+        <v>234.5866504343669</v>
       </c>
       <c r="D6" t="n">
-        <v>58.04288777047993</v>
+        <v>67.50202690089796</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>136.3019242668101</v>
+        <v>113.1258062126557</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>66.7588438887831</v>
+        <v>54.82570054366312</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.374266859496287</v>
+        <v>0.2493639168786898</v>
       </c>
       <c r="C2" t="n">
-        <v>1.716094987023425</v>
+        <v>3.721805546799658</v>
       </c>
       <c r="D2" t="n">
-        <v>22.83839684389355</v>
+        <v>7.459319056867265</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8811517745239</v>
+        <v>2.807798434145878</v>
       </c>
       <c r="C3" t="n">
-        <v>14.07335334037803</v>
+        <v>28.64739800992193</v>
       </c>
       <c r="D3" t="n">
-        <v>87.29209712310515</v>
+        <v>52.46950605347078</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.48258756879548</v>
+        <v>12.34155039008665</v>
       </c>
       <c r="C4" t="n">
-        <v>77.22721965916685</v>
+        <v>78.46520351422208</v>
       </c>
       <c r="D4" t="n">
-        <v>178.5504549713674</v>
+        <v>124.0153517481613</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.69530802544756</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C5" t="n">
-        <v>200.3010753589555</v>
+        <v>171.3640617762808</v>
       </c>
       <c r="D5" t="n">
-        <v>155.680642200938</v>
+        <v>123.2338805755809</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.86801350593698</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>268.2370347451306</v>
+        <v>239.6583590745059</v>
       </c>
       <c r="D6" t="n">
-        <v>78.24921901928779</v>
+        <v>71.64794745593223</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>206.7285775786594</v>
+        <v>153.369608105141</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>113.3231375012093</v>
+        <v>62.16917337142927</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.303180114163017</v>
+        <v>0.1757328390601791</v>
       </c>
       <c r="C2" t="n">
-        <v>2.021418523044182</v>
+        <v>5.576326960121882</v>
       </c>
       <c r="D2" t="n">
-        <v>15.93376523992573</v>
+        <v>12.27479154619787</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7900291644782</v>
+        <v>1.742602175038088</v>
       </c>
       <c r="C3" t="n">
-        <v>10.85322087044849</v>
+        <v>20.18473279931442</v>
       </c>
       <c r="D3" t="n">
-        <v>86.60487373013238</v>
+        <v>46.76555189179681</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.11322944782042</v>
+        <v>8.70417514585222</v>
       </c>
       <c r="C4" t="n">
-        <v>61.4524975473291</v>
+        <v>75.3638625165064</v>
       </c>
       <c r="D4" t="n">
-        <v>180.8732700396153</v>
+        <v>121.3096550752571</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.51216317310991</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C5" t="n">
-        <v>185.4275976396163</v>
+        <v>156.981457909065</v>
       </c>
       <c r="D5" t="n">
-        <v>172.2476347101029</v>
+        <v>140.4880964777186</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.11331156327844</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C6" t="n">
-        <v>297.5402402214894</v>
+        <v>260.3879618496773</v>
       </c>
       <c r="D6" t="n">
-        <v>94.87315289529903</v>
+        <v>93.18258334858602</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>264.0400633094754</v>
+        <v>252.841267247132</v>
       </c>
       <c r="D7" t="n">
-        <v>47.49008169753095</v>
+        <v>46.95110220789945</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>153.4618923893402</v>
+        <v>134.0183791067321</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>55.02499532762521</v>
+        <v>53.24999547834697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>23.18593553119691</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.565707661824415</v>
+        <v>0.8158323422290994</v>
       </c>
       <c r="C2" t="n">
-        <v>10.79137076508094</v>
+        <v>8.046404184006859</v>
       </c>
       <c r="D2" t="n">
-        <v>29.38763577892402</v>
+        <v>16.27344994559513</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.47172192412398</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C3" t="n">
-        <v>9.390416791120741</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D3" t="n">
-        <v>80.22842239104935</v>
+        <v>45.65126824747668</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.68907338185679</v>
+        <v>5.998478472948012</v>
       </c>
       <c r="C4" t="n">
-        <v>46.12447064092365</v>
+        <v>62.14168443571036</v>
       </c>
       <c r="D4" t="n">
-        <v>181.7411350101695</v>
+        <v>117.6595171108675</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.97849333262715</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C5" t="n">
-        <v>154.4534575706295</v>
+        <v>147.8021168743573</v>
       </c>
       <c r="D5" t="n">
-        <v>190.6063167795183</v>
+        <v>150.0110492089127</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.82025202579416</v>
+        <v>22.90319219237384</v>
       </c>
       <c r="C6" t="n">
-        <v>297.5402402214894</v>
+        <v>256.3225446063913</v>
       </c>
       <c r="D6" t="n">
-        <v>117.0518152819387</v>
+        <v>114.2744510266245</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.02126395879071</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>333.0294379823072</v>
+        <v>314.7041353348363</v>
       </c>
       <c r="D7" t="n">
-        <v>57.97023844036566</v>
+        <v>60.84479571840032</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>226.8966206670016</v>
+        <v>230.2345628614407</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>103.6156162016168</v>
+        <v>105.8343660132146</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>25.4046853427947</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.674100819919064</v>
+        <v>5.279839153439347</v>
       </c>
       <c r="C2" t="n">
-        <v>2.634029090494193</v>
+        <v>5.407466354991432</v>
       </c>
       <c r="D2" t="n">
-        <v>15.85031668506475</v>
+        <v>12.46917759163874</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.580032966760618</v>
+        <v>0.7078400947619502</v>
       </c>
       <c r="C2" t="n">
-        <v>6.215444715586557</v>
+        <v>10.31325963311274</v>
       </c>
       <c r="D2" t="n">
-        <v>21.86352137357647</v>
+        <v>19.43369580556561</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.51652246562084</v>
+        <v>1.894773069196344</v>
       </c>
       <c r="C3" t="n">
-        <v>20.19945901487813</v>
+        <v>26.09485397888022</v>
       </c>
       <c r="D3" t="n">
-        <v>89.94281592457153</v>
+        <v>47.22697331279281</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.08618248045802</v>
+        <v>4.147884050442774</v>
       </c>
       <c r="C4" t="n">
-        <v>72.05831799630738</v>
+        <v>56.75581653021235</v>
       </c>
       <c r="D4" t="n">
-        <v>186.0421717024748</v>
+        <v>113.103226015458</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.34291735288518</v>
+        <v>13.49903093339365</v>
       </c>
       <c r="C5" t="n">
-        <v>243.3507121901782</v>
+        <v>132.2168720694392</v>
       </c>
       <c r="D5" t="n">
-        <v>172.1985473248906</v>
+        <v>157.1532637573082</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.24029150782899</v>
+        <v>23.14470212761856</v>
       </c>
       <c r="C6" t="n">
-        <v>274.7578029967379</v>
+        <v>245.5351008321273</v>
       </c>
       <c r="D6" t="n">
-        <v>90.56622571676827</v>
+        <v>131.7034180201181</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>159.5379289309237</v>
+        <v>342.6112955757561</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>74.55882939902401</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>76.35542769779568</v>
+        <v>313.7665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>181.2718596075395</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>77.58261232810419</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.015569094547707</v>
+        <v>4.236241343824987</v>
       </c>
       <c r="C2" t="n">
-        <v>5.072690387843269</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="D2" t="n">
-        <v>19.30115986549229</v>
+        <v>22.08048761621501</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.935286766977722</v>
+        <v>8.717919613711677</v>
       </c>
       <c r="C3" t="n">
-        <v>6.636614480708438</v>
+        <v>10.67650628368406</v>
       </c>
       <c r="D3" t="n">
-        <v>16.44918278465531</v>
+        <v>11.52080930933632</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39802622383029</v>
+        <v>11.67806767199781</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14260787769973</v>
+        <v>59.94741404958878</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576238379274151</v>
+        <v>0.7785378447998543</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.114905539125882</v>
+        <v>2.615375884113503</v>
       </c>
       <c r="C2" t="n">
-        <v>4.286310476741575</v>
+        <v>4.803691516879643</v>
       </c>
       <c r="D2" t="n">
-        <v>21.74276640595411</v>
+        <v>21.92733497435251</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.45685683984004</v>
+        <v>12.56637061435917</v>
       </c>
       <c r="C3" t="n">
-        <v>14.85875150377547</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="D3" t="n">
-        <v>28.6866679180918</v>
+        <v>28.0534406488526</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.65236350170539</v>
+        <v>10.79726125130642</v>
       </c>
       <c r="C4" t="n">
-        <v>10.66963404975434</v>
+        <v>17.91885909791278</v>
       </c>
       <c r="D4" t="n">
-        <v>23.68760860806704</v>
+        <v>20.31825048709199</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44202005236402</v>
+        <v>13.62908433914595</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15021713424139</v>
+        <v>73.75739760008398</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250951589971373</v>
+        <v>1.603421686958347</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.583780031128358</v>
+        <v>2.608503650183775</v>
       </c>
       <c r="C2" t="n">
-        <v>4.726133448244146</v>
+        <v>3.310453258720245</v>
       </c>
       <c r="D2" t="n">
-        <v>33.09766035327272</v>
+        <v>18.79457805010094</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04452280405637</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="C3" t="n">
-        <v>15.96321767105314</v>
+        <v>21.27938148954962</v>
       </c>
       <c r="D3" t="n">
-        <v>39.42207906403067</v>
+        <v>39.69205968269855</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.19360958638165</v>
+        <v>19.06750391188155</v>
       </c>
       <c r="C4" t="n">
-        <v>26.27844079957437</v>
+        <v>45.80540263704343</v>
       </c>
       <c r="D4" t="n">
-        <v>32.73637719810989</v>
+        <v>30.29869764846506</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.70104997629023</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>13.49903093339365</v>
+        <v>21.86843011209771</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92505268377453</v>
+        <v>27.243498792849</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73878723431325</v>
+        <v>14.84066049374262</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1066021293108</v>
+        <v>87.39500068537319</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021636170293975</v>
+        <v>2.473443415623769</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.15221195188726</v>
+        <v>2.457314503729767</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1408729477928</v>
+        <v>6.992988897350031</v>
       </c>
       <c r="D2" t="n">
-        <v>32.87676711981719</v>
+        <v>20.28879805596458</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.76334205001429</v>
+        <v>9.719302272043423</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5143790437631</v>
+        <v>16.11538856521139</v>
       </c>
       <c r="D3" t="n">
-        <v>55.80744824790993</v>
+        <v>45.51873230740336</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.37527396939631</v>
+        <v>20.15233512507428</v>
       </c>
       <c r="C4" t="n">
-        <v>33.65529304928491</v>
+        <v>50.33616829214247</v>
       </c>
       <c r="D4" t="n">
-        <v>44.14624901686633</v>
+        <v>43.07418052382881</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.51914891356409</v>
+        <v>19.88039101099791</v>
       </c>
       <c r="C5" t="n">
-        <v>32.7658296292373</v>
+        <v>58.26672624704821</v>
       </c>
       <c r="D5" t="n">
-        <v>35.80924751240241</v>
+        <v>32.34858685493241</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>9.378635818669782</v>
       </c>
       <c r="C6" t="n">
-        <v>17.10695374650067</v>
+        <v>23.98998690097506</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06908677064635</v>
+        <v>16.08686182050555</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8792803608834</v>
+        <v>101.6012325505614</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883461626912896</v>
+        <v>3.38670775168538</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.183047041346412</v>
+        <v>3.646210973572654</v>
       </c>
       <c r="C2" t="n">
-        <v>10.38394546781851</v>
+        <v>8.355654710844604</v>
       </c>
       <c r="D2" t="n">
-        <v>27.48206348498096</v>
+        <v>24.44060909722434</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.44780012632356</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="C3" t="n">
-        <v>30.62071089545801</v>
+        <v>22.59492341324034</v>
       </c>
       <c r="D3" t="n">
-        <v>64.32901832077225</v>
+        <v>50.81035243329367</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.11328620108265</v>
+        <v>19.38657191576176</v>
       </c>
       <c r="C4" t="n">
-        <v>33.06820792214531</v>
+        <v>44.66952054322987</v>
       </c>
       <c r="D4" t="n">
-        <v>53.06739040535709</v>
+        <v>55.07113746972482</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.52481841561132</v>
+        <v>25.45180923259857</v>
       </c>
       <c r="C5" t="n">
-        <v>36.32466505713199</v>
+        <v>77.38626278725484</v>
       </c>
       <c r="D5" t="n">
-        <v>35.39200473809752</v>
+        <v>40.57072387799944</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>18.19374845510189</v>
       </c>
       <c r="C6" t="n">
-        <v>23.82898027747859</v>
+        <v>60.13597387593413</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>14.85187926984575</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064166003730895</v>
+        <v>17.36162319875353</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22655628497714</v>
+        <v>115.454794271711</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298124502798172</v>
+        <v>4.340405799688384</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.765403356414017</v>
+        <v>2.626175108860218</v>
       </c>
       <c r="C2" t="n">
-        <v>6.505060288339365</v>
+        <v>11.83202333158256</v>
       </c>
       <c r="D2" t="n">
-        <v>21.87922933684441</v>
+        <v>32.30538995594554</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29134238844982</v>
+        <v>10.82867717784232</v>
       </c>
       <c r="C3" t="n">
-        <v>37.16405934426301</v>
+        <v>28.0239882177252</v>
       </c>
       <c r="D3" t="n">
-        <v>72.34989706446869</v>
+        <v>57.59422906963913</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.58023825540564</v>
+        <v>18.48041878474196</v>
       </c>
       <c r="C4" t="n">
-        <v>60.96751418143117</v>
+        <v>51.02535518052373</v>
       </c>
       <c r="D4" t="n">
-        <v>75.56806603898974</v>
+        <v>66.17470400475625</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.62423697564751</v>
+        <v>27.29258617806133</v>
       </c>
       <c r="C5" t="n">
-        <v>51.78719139901926</v>
+        <v>80.01243789611506</v>
       </c>
       <c r="D5" t="n">
-        <v>47.73748211900116</v>
+        <v>50.60909415392309</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.05790741901734</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="C6" t="n">
-        <v>44.11581483803468</v>
+        <v>90.96874227550947</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>26.52976821186155</v>
+        <v>56.65273302126644</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>19.69385894719101</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288784675082328</v>
+        <v>18.65834463225272</v>
       </c>
       <c r="C21" t="n">
-        <v>75.62114100397915</v>
+        <v>128.8314272226974</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377686590697037</v>
+        <v>5.330955609215063</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.477170441992955</v>
+        <v>2.432770811123596</v>
       </c>
       <c r="C2" t="n">
-        <v>9.725192758268904</v>
+        <v>7.193265429016379</v>
       </c>
       <c r="D2" t="n">
-        <v>33.53650157707104</v>
+        <v>25.28982086139784</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7450897542611</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C3" t="n">
-        <v>29.87949137875168</v>
+        <v>44.66461180470864</v>
       </c>
       <c r="D3" t="n">
-        <v>73.06657288856887</v>
+        <v>65.14386891529711</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.57871672835365</v>
+        <v>13.10731359939917</v>
       </c>
       <c r="C4" t="n">
-        <v>80.22645889564085</v>
+        <v>72.26252151879073</v>
       </c>
       <c r="D4" t="n">
-        <v>94.15058658497337</v>
+        <v>62.52456604036662</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.47192721276901</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="C5" t="n">
-        <v>87.1546524445106</v>
+        <v>54.33973543006097</v>
       </c>
       <c r="D5" t="n">
-        <v>65.01624171374503</v>
+        <v>39.56443248114646</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.83905979642831</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>65.52969576306612</v>
+        <v>37.31328499530853</v>
       </c>
       <c r="D6" t="n">
-        <v>43.19002675292993</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>47.19064864773568</v>
+        <v>21.43940636534185</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>28.28906009787184</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>24.73906039931537</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.501179896962925</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.32592132795327</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.501179896962925</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
